--- a/assets/constructions/examples/ctd_mic_90.xlsx
+++ b/assets/constructions/examples/ctd_mic_90.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MT190-032MK3R04BO12</t>
+          <t>MT190-025MK3R02BO12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -597,7 +617,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
         <v>19</v>
@@ -611,20 +631,20 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="N2" t="n">
         <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -673,11 +693,17 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT190-054C05R05BD10-H080-IK</t>
+          <t>MT190-032C04R03BD10-h040-H065-IK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -691,31 +717,33 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>110</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="H3" t="n">
+        <v>40</v>
+      </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>22700</v>
+        <v>31000</v>
       </c>
       <c r="N3" t="n">
-        <v>1.6</v>
+        <v>0.54</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
@@ -731,7 +759,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ISO_26623:50</t>
+          <t>ISO_26623:40</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -767,11 +795,17 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT190-025C05R04BD10-h125-H150-IK</t>
+          <t>MT190-054C05R05BD10-H080-IK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -785,33 +819,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="E4" t="n">
         <v>50</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>180</v>
-      </c>
-      <c r="H4" t="n">
-        <v>125</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>20000</v>
+        <v>22700</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="O4" t="n">
         <v>10</v>
@@ -863,11 +895,17 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT190-032C06R04BD10-h096-H165-IK</t>
+          <t>MT190-044C04R04BD10-H075-IK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -881,20 +919,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>203</v>
-      </c>
-      <c r="H5" t="n">
-        <v>96</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -904,10 +940,10 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>20000</v>
+        <v>25600</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>0.88</v>
       </c>
       <c r="O5" t="n">
         <v>10</v>
@@ -923,7 +959,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ISO_26623:63</t>
+          <t>ISO_26623:40</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -959,11 +995,17 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT190-040C06R06BD10-h120-H165-IK</t>
+          <t>MT190-016C03R02BD10-h025-H050-IK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -977,33 +1019,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>203</v>
+        <v>69</v>
       </c>
       <c r="H6" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>20000</v>
+        <v>39000</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>0.28</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
@@ -1019,7 +1061,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ISO_26623:63</t>
+          <t>ISO_26623:32</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1055,6 +1097,12 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
